--- a/data/trans_orig/P57B3_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P57B3_R-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3744</t>
+          <t>4161</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1122</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9576</t>
+          <t>9192</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4624</t>
+          <t>5013</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2139</t>
+          <t>2471</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7835</t>
+          <t>9056</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>8367</t>
+          <t>9174</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4528</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13555</t>
+          <t>15408</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>307699</t>
+          <t>314684</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>301867</t>
+          <t>309653</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>310321</t>
+          <t>317477</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>285011</t>
+          <t>311048</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>281800</t>
+          <t>307005</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>287496</t>
+          <t>313590</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>592710</t>
+          <t>625732</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>587522</t>
+          <t>619498</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>596549</t>
+          <t>629600</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,16%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>39733</t>
+          <t>40884</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26314</t>
+          <t>28547</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55433</t>
+          <t>56848</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>51849</t>
+          <t>55387</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40812</t>
+          <t>43899</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>65589</t>
+          <t>70108</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>91582</t>
+          <t>96271</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>73034</t>
+          <t>77452</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>111617</t>
+          <t>115519</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>477789</t>
+          <t>488835</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>462089</t>
+          <t>472871</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>491208</t>
+          <t>501172</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>462028</t>
+          <t>489924</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>448288</t>
+          <t>475203</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>473065</t>
+          <t>501412</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>939817</t>
+          <t>978759</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>919782</t>
+          <t>959511</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>958365</t>
+          <t>997578</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,8%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>517522</t>
+          <t>529719</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>517522</t>
+          <t>529719</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>517522</t>
+          <t>529719</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>513877</t>
+          <t>545311</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>513877</t>
+          <t>545311</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>513877</t>
+          <t>545311</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1031399</t>
+          <t>1075030</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1031399</t>
+          <t>1075030</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1031399</t>
+          <t>1075030</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>33633</t>
+          <t>35420</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24747</t>
+          <t>26117</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44876</t>
+          <t>46282</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>47022</t>
+          <t>51024</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37992</t>
+          <t>41237</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57184</t>
+          <t>61433</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>80656</t>
+          <t>86444</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>67717</t>
+          <t>73059</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>96498</t>
+          <t>101893</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>15,15%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>282417</t>
+          <t>280573</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>271174</t>
+          <t>269711</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>291303</t>
+          <t>289876</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>302106</t>
+          <t>305357</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>291944</t>
+          <t>294948</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>311136</t>
+          <t>315144</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>584522</t>
+          <t>585931</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>568680</t>
+          <t>570482</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>597461</t>
+          <t>599316</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,13%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17463</t>
+          <t>18649</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10161</t>
+          <t>10823</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28562</t>
+          <t>30590</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>31237</t>
+          <t>36052</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17836</t>
+          <t>27495</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45036</t>
+          <t>50439</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>48699</t>
+          <t>54701</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33297</t>
+          <t>42203</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>65849</t>
+          <t>72874</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>9,19%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>295094</t>
+          <t>354496</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>283995</t>
+          <t>342555</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>302396</t>
+          <t>362322</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>442764</t>
+          <t>384085</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>428965</t>
+          <t>369698</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>456165</t>
+          <t>392642</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>737859</t>
+          <t>738582</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>720709</t>
+          <t>720409</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>753261</t>
+          <t>751080</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>94,68%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>474001</t>
+          <t>420137</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>474001</t>
+          <t>420137</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>474001</t>
+          <t>420137</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>786558</t>
+          <t>793283</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>786558</t>
+          <t>793283</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>786558</t>
+          <t>793283</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>25641</t>
+          <t>31043</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18687</t>
+          <t>22839</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34363</t>
+          <t>41381</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>23576</t>
+          <t>26613</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17830</t>
+          <t>21063</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29697</t>
+          <t>34308</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>49217</t>
+          <t>57656</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>40406</t>
+          <t>47949</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>60753</t>
+          <t>69435</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>16,05%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>153101</t>
+          <t>174622</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>144379</t>
+          <t>164284</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>160055</t>
+          <t>182826</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>184698</t>
+          <t>200210</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>178577</t>
+          <t>192515</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>190444</t>
+          <t>205760</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>337799</t>
+          <t>374832</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>326263</t>
+          <t>363053</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>346610</t>
+          <t>384539</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>88,91%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208274</t>
+          <t>226823</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>387016</t>
+          <t>432488</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>40916</t>
+          <t>43576</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>32255</t>
+          <t>33924</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>51240</t>
+          <t>54244</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>34510</t>
+          <t>36700</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28474</t>
+          <t>29580</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41904</t>
+          <t>45384</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>75426</t>
+          <t>80276</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>64166</t>
+          <t>69917</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>88483</t>
+          <t>95638</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>17,89%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>228720</t>
+          <t>227131</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>218396</t>
+          <t>216463</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>237381</t>
+          <t>236783</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>222546</t>
+          <t>227050</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>215152</t>
+          <t>218366</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>228582</t>
+          <t>234170</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>451266</t>
+          <t>454181</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>438209</t>
+          <t>438819</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>462526</t>
+          <t>464540</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>86,92%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>49829</t>
+          <t>61387</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>37709</t>
+          <t>47300</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>65654</t>
+          <t>78974</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>61185</t>
+          <t>74438</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28185</t>
+          <t>59649</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>86742</t>
+          <t>92297</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>111014</t>
+          <t>135825</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>65685</t>
+          <t>116178</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>136134</t>
+          <t>158430</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>10,64%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>574450</t>
+          <t>658300</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>558625</t>
+          <t>640713</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>586570</t>
+          <t>672387</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>785447</t>
+          <t>694827</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>759890</t>
+          <t>676968</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>818447</t>
+          <t>709616</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1359897</t>
+          <t>1353127</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1334777</t>
+          <t>1330522</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1405226</t>
+          <t>1372774</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>92,2%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>846632</t>
+          <t>769265</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>846632</t>
+          <t>769265</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>846632</t>
+          <t>769265</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1470911</t>
+          <t>1488952</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1470911</t>
+          <t>1488952</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1470911</t>
+          <t>1488952</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>398375</t>
+          <t>181919</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>199678</t>
+          <t>159947</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>682821</t>
+          <t>207710</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>186487</t>
+          <t>219580</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>168202</t>
+          <t>198017</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>207670</t>
+          <t>243292</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>584863</t>
+          <t>401499</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>388937</t>
+          <t>369757</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>980872</t>
+          <t>435253</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>26,73%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>529320</t>
+          <t>614999</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>244874</t>
+          <t>589208</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>728017</t>
+          <t>636971</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>57,06%</t>
+          <t>77,17%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>531244</t>
+          <t>611751</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>510061</t>
+          <t>588039</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>549529</t>
+          <t>633314</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>70,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>76,18%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1060563</t>
+          <t>1226750</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>664554</t>
+          <t>1192996</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1256489</t>
+          <t>1258492</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>64,46%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>77,29%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>927695</t>
+          <t>796918</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>927695</t>
+          <t>796918</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>927695</t>
+          <t>796918</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1645426</t>
+          <t>1628249</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1645426</t>
+          <t>1628249</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1645426</t>
+          <t>1628249</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3469,32 +3469,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>609334</t>
+          <t>417039</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>379463</t>
+          <t>378278</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1280857</t>
+          <t>460031</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,32 +3504,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>440490</t>
+          <t>504807</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>358236</t>
+          <t>470570</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>482937</t>
+          <t>542857</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1049824</t>
+          <t>921846</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>820712</t>
+          <t>872490</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1872786</t>
+          <t>975451</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>13,44%</t>
         </is>
       </c>
     </row>
@@ -3582,32 +3582,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2848590</t>
+          <t>3113641</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2177067</t>
+          <t>3070649</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3078461</t>
+          <t>3152402</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>62,96%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,32 +3617,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3215843</t>
+          <t>3224253</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3173396</t>
+          <t>3186203</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3298097</t>
+          <t>3258490</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>85,44%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6064433</t>
+          <t>6337894</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5241471</t>
+          <t>6284289</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6293545</t>
+          <t>6387250</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>87,98%</t>
         </is>
       </c>
     </row>
@@ -3695,17 +3695,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3457924</t>
+          <t>3530680</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3457924</t>
+          <t>3530680</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3457924</t>
+          <t>3530680</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3730,17 +3730,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3656333</t>
+          <t>3729060</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3656333</t>
+          <t>3729060</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3656333</t>
+          <t>3729060</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7114257</t>
+          <t>7259740</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7114257</t>
+          <t>7259740</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7114257</t>
+          <t>7259740</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
